--- a/resources/formatos/FormatoPiezometroCuerda.xlsx
+++ b/resources/formatos/FormatoPiezometroCuerda.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\E-Monitoring-SqlServer\resources\formatos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\E-Monitoring-SqlServer\resources\formatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4693C2B7-4BD3-4A42-B432-B52DE8A07779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FC5B63-B2A1-462F-919E-3DA7D40229A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Piezometro" sheetId="1" r:id="rId1"/>
@@ -39,33 +39,21 @@
     <t>Nombre:</t>
   </si>
   <si>
-    <t>Cota Instalación (m.s.n.m):</t>
-  </si>
-  <si>
     <t>C.F.:</t>
   </si>
   <si>
-    <t>Cota Fundación (m.s.n.m):</t>
-  </si>
-  <si>
     <t>T.K.:</t>
   </si>
   <si>
     <t>Coordenada Este:</t>
   </si>
   <si>
-    <t>Inclinación:</t>
-  </si>
-  <si>
     <t>Serie:</t>
   </si>
   <si>
     <t>Coordenada Norte:</t>
   </si>
   <si>
-    <t>Azimuth:</t>
-  </si>
-  <si>
     <t>Fecha</t>
   </si>
   <si>
@@ -87,24 +75,15 @@
     <t>FORMATO DE DATOS - PIEZÓMETROS CUERDA VIBRANTE</t>
   </si>
   <si>
-    <t>Cota de Superficie Actual (m.s.n.m):</t>
-  </si>
-  <si>
     <t>Piezometro1</t>
   </si>
   <si>
     <t>Serie1</t>
   </si>
   <si>
-    <t>Frecuencia Inicial (Dg):</t>
-  </si>
-  <si>
     <t>Temperatura Inicial (°C):</t>
   </si>
   <si>
-    <t>Presión Inicial:</t>
-  </si>
-  <si>
     <t>Factor de Conversión:</t>
   </si>
   <si>
@@ -117,9 +96,6 @@
     <t>Constante C:</t>
   </si>
   <si>
-    <t>Frecuencia (Dg)</t>
-  </si>
-  <si>
     <t>Presión (kPa)</t>
   </si>
   <si>
@@ -127,6 +103,30 @@
   </si>
   <si>
     <t>* El formato de hora: hh:mm:ss</t>
+  </si>
+  <si>
+    <t>Cota Instalación (msnm):</t>
+  </si>
+  <si>
+    <t>Cota Fundación (msnm):</t>
+  </si>
+  <si>
+    <t>Cota de Superficie Actual (msnm):</t>
+  </si>
+  <si>
+    <t>Inclinación (°):</t>
+  </si>
+  <si>
+    <t>Azimuth (°):</t>
+  </si>
+  <si>
+    <t>Frecuencia Inicial (digits):</t>
+  </si>
+  <si>
+    <t>Presión Inicial (kPa):</t>
+  </si>
+  <si>
+    <t>Frecuencia (digits)</t>
   </si>
 </sst>
 </file>
@@ -136,7 +136,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,6 +169,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -448,7 +455,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -471,6 +478,55 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -497,51 +553,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -888,245 +899,245 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19"/>
-      <c r="B1" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="26"/>
-    </row>
-    <row r="2" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="20"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="24"/>
-    </row>
-    <row r="3" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="20"/>
-      <c r="B3" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="32"/>
-    </row>
-    <row r="4" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="21"/>
-      <c r="B4" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="32"/>
-    </row>
-    <row r="5" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="27"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="29"/>
-    </row>
-    <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="15" t="s">
+    <row r="1" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14"/>
+      <c r="B1" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="18"/>
+    </row>
+    <row r="2" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="20"/>
+    </row>
+    <row r="3" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15"/>
+      <c r="B3" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="23"/>
+    </row>
+    <row r="4" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16"/>
+      <c r="B4" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="24"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="26"/>
+    </row>
+    <row r="6" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="30"/>
+      <c r="C6" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="15" t="s">
+      <c r="D6" s="33"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="16"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="14"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="16"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G6" s="33"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="31"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="33"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="11"/>
+        <v>16</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="28"/>
       <c r="E8" s="6">
         <v>0</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G8" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="11"/>
+        <v>17</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="28"/>
       <c r="E9" s="6">
         <v>90</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>25</v>
+      <c r="F9" s="12" t="s">
+        <v>32</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4">
+        <v>0</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="28"/>
+      <c r="E10" s="6">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="4">
-        <v>0</v>
-      </c>
-      <c r="C10" s="10" t="s">
+      <c r="B11" s="4">
+        <v>0</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="28"/>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="4">
+        <v>0</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="28"/>
+      <c r="E12" s="8">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="4">
+        <v>0</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="28"/>
+      <c r="E13" s="7">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="6">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="4">
-        <v>0</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="6">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="4">
-        <v>0</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="8">
-        <v>0</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="4">
-        <v>0</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="7">
-        <v>0</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+      <c r="G14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="11">
+        <v>44166</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="33">
-        <v>44166</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>18</v>
-      </c>
       <c r="C15">
         <v>0</v>
       </c>
@@ -1140,12 +1151,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="33">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="11">
         <v>44180</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>18</v>
+      <c r="B16" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1162,20 +1173,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="F6:G7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C12:D12"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A6:B7"/>
     <mergeCell ref="C6:E7"/>
-    <mergeCell ref="F6:G7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C12:D12"/>
     <mergeCell ref="A1:A4"/>
     <mergeCell ref="B1:G2"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B4:G4"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
